--- a/PL_Year1月次_大成功_v2.xlsx
+++ b/PL_Year1月次_大成功_v2.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -80,6 +80,17 @@
     </font>
     <font>
       <name val="Meiryo UI"/>
+      <color rgb="00888888"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <b val="1"/>
+      <color rgb="00888888"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Meiryo UI"/>
       <b val="1"/>
       <color rgb="001A3A6B"/>
       <sz val="9"/>
@@ -131,7 +142,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -166,6 +177,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E5E7E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FAFAFA"/>
       </patternFill>
     </fill>
     <fill>
@@ -220,7 +236,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -275,62 +291,74 @@
     <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="3" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="12" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="3" fontId="14" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="13" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="3" fontId="14" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="16" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="3" fontId="17" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="17" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="3" fontId="14" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="16" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="4" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
@@ -698,7 +726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N49"/>
+  <dimension ref="A1:N55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1305,102 +1333,110 @@
         <v>3800</v>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ② IGメディアタイアップ</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="18" t="n">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     受注社数（社）</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="L16" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M16" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="N16" s="22" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     平均単価（万円/社）</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="n">
         <v>100</v>
       </c>
-      <c r="F16" s="18" t="n">
+      <c r="E17" s="21" t="n">
         <v>150</v>
       </c>
-      <c r="G16" s="18" t="n">
-        <v>200</v>
-      </c>
-      <c r="H16" s="18" t="n">
-        <v>300</v>
-      </c>
-      <c r="I16" s="18" t="n">
-        <v>350</v>
-      </c>
-      <c r="J16" s="18" t="n">
-        <v>400</v>
-      </c>
-      <c r="K16" s="18" t="n">
-        <v>500</v>
-      </c>
-      <c r="L16" s="18" t="n">
-        <v>500</v>
-      </c>
-      <c r="M16" s="18" t="n">
-        <v>600</v>
-      </c>
-      <c r="N16" s="14" t="n">
-        <v>3100</v>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  タイアップ売上合計</t>
-        </is>
-      </c>
-      <c r="B17" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="20" t="n">
+      <c r="F17" s="21" t="n">
         <v>100</v>
       </c>
-      <c r="E17" s="20" t="n">
-        <v>250</v>
-      </c>
-      <c r="F17" s="20" t="n">
-        <v>350</v>
-      </c>
-      <c r="G17" s="20" t="n">
-        <v>500</v>
-      </c>
-      <c r="H17" s="20" t="n">
-        <v>650</v>
-      </c>
-      <c r="I17" s="20" t="n">
-        <v>750</v>
-      </c>
-      <c r="J17" s="20" t="n">
-        <v>900</v>
-      </c>
-      <c r="K17" s="20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L17" s="20" t="n">
-        <v>1100</v>
-      </c>
-      <c r="M17" s="20" t="n">
-        <v>1300</v>
-      </c>
-      <c r="N17" s="20" t="n">
-        <v>6900</v>
+      <c r="G17" s="21" t="n">
+        <v>150</v>
+      </c>
+      <c r="H17" s="21" t="n">
+        <v>117</v>
+      </c>
+      <c r="I17" s="21" t="n">
+        <v>133</v>
+      </c>
+      <c r="J17" s="21" t="n">
+        <v>125</v>
+      </c>
+      <c r="K17" s="21" t="n">
+        <v>125</v>
+      </c>
+      <c r="L17" s="21" t="n">
+        <v>120</v>
+      </c>
+      <c r="M17" s="21" t="n">
+        <v>140</v>
+      </c>
+      <c r="N17" s="22" t="n">
+        <v>126</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ③ TikTok Shop / WESELL EC売上</t>
+          <t xml:space="preserve">  ② IGメディアタイアップ</t>
         </is>
       </c>
       <c r="B18" s="18" t="n">
@@ -1410,125 +1446,193 @@
         <v>0</v>
       </c>
       <c r="D18" s="18" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="F18" s="18" t="n">
         <v>150</v>
       </c>
       <c r="G18" s="18" t="n">
-        <v>292</v>
+        <v>200</v>
       </c>
       <c r="H18" s="18" t="n">
-        <v>490</v>
+        <v>300</v>
       </c>
       <c r="I18" s="18" t="n">
-        <v>720</v>
+        <v>350</v>
       </c>
       <c r="J18" s="18" t="n">
-        <v>975</v>
+        <v>400</v>
       </c>
       <c r="K18" s="18" t="n">
-        <v>1326</v>
+        <v>500</v>
       </c>
       <c r="L18" s="18" t="n">
-        <v>1760</v>
+        <v>500</v>
       </c>
       <c r="M18" s="18" t="n">
-        <v>2296</v>
+        <v>600</v>
       </c>
       <c r="N18" s="14" t="n">
-        <v>8100</v>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="21" t="inlineStr">
-        <is>
-          <t>売上合計</t>
-        </is>
-      </c>
-      <c r="B19" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="22" t="n">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     受注社数（社）</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="L19" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="M19" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="N19" s="22" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     平均単価（万円/社）</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="n">
+        <v>100</v>
+      </c>
+      <c r="F20" s="21" t="n">
+        <v>150</v>
+      </c>
+      <c r="G20" s="21" t="n">
+        <v>100</v>
+      </c>
+      <c r="H20" s="21" t="n">
+        <v>150</v>
+      </c>
+      <c r="I20" s="21" t="n">
+        <v>117</v>
+      </c>
+      <c r="J20" s="21" t="n">
+        <v>133</v>
+      </c>
+      <c r="K20" s="21" t="n">
         <v>125</v>
       </c>
-      <c r="E19" s="22" t="n">
-        <v>316</v>
-      </c>
-      <c r="F19" s="22" t="n">
+      <c r="L20" s="21" t="n">
+        <v>125</v>
+      </c>
+      <c r="M20" s="21" t="n">
+        <v>120</v>
+      </c>
+      <c r="N20" s="22" t="n">
+        <v>124.4</v>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  タイアップ売上合計</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="24" t="n">
+        <v>100</v>
+      </c>
+      <c r="E21" s="24" t="n">
+        <v>250</v>
+      </c>
+      <c r="F21" s="24" t="n">
+        <v>350</v>
+      </c>
+      <c r="G21" s="24" t="n">
         <v>500</v>
       </c>
-      <c r="G19" s="22" t="n">
-        <v>792</v>
-      </c>
-      <c r="H19" s="22" t="n">
-        <v>1140</v>
-      </c>
-      <c r="I19" s="22" t="n">
-        <v>1470</v>
-      </c>
-      <c r="J19" s="22" t="n">
-        <v>1875</v>
-      </c>
-      <c r="K19" s="22" t="n">
-        <v>2326</v>
-      </c>
-      <c r="L19" s="22" t="n">
-        <v>2860</v>
-      </c>
-      <c r="M19" s="22" t="n">
-        <v>3596</v>
-      </c>
-      <c r="N19" s="22" t="n">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="20" ht="6" customHeight="1">
-      <c r="A20" s="23" t="inlineStr"/>
-      <c r="B20" s="24" t="n"/>
-      <c r="C20" s="24" t="n"/>
-      <c r="D20" s="24" t="n"/>
-      <c r="E20" s="24" t="n"/>
-      <c r="F20" s="24" t="n"/>
-      <c r="G20" s="24" t="n"/>
-      <c r="H20" s="24" t="n"/>
-      <c r="I20" s="24" t="n"/>
-      <c r="J20" s="24" t="n"/>
-      <c r="K20" s="24" t="n"/>
-      <c r="L20" s="24" t="n"/>
-      <c r="M20" s="24" t="n"/>
-      <c r="N20" s="24" t="n"/>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t>【タイアップ原価】※ほぼライセンス料のみ</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="n"/>
-      <c r="C21" s="17" t="n"/>
-      <c r="D21" s="17" t="n"/>
-      <c r="E21" s="17" t="n"/>
-      <c r="F21" s="17" t="n"/>
-      <c r="G21" s="17" t="n"/>
-      <c r="H21" s="17" t="n"/>
-      <c r="I21" s="17" t="n"/>
-      <c r="J21" s="17" t="n"/>
-      <c r="K21" s="17" t="n"/>
-      <c r="L21" s="17" t="n"/>
-      <c r="M21" s="17" t="n"/>
-      <c r="N21" s="17" t="n"/>
+      <c r="H21" s="24" t="n">
+        <v>650</v>
+      </c>
+      <c r="I21" s="24" t="n">
+        <v>750</v>
+      </c>
+      <c r="J21" s="24" t="n">
+        <v>900</v>
+      </c>
+      <c r="K21" s="24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L21" s="24" t="n">
+        <v>1100</v>
+      </c>
+      <c r="M21" s="24" t="n">
+        <v>1300</v>
+      </c>
+      <c r="N21" s="24" t="n">
+        <v>6900</v>
+      </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ギャル協会ライセンス料（タイアップ×20%）</t>
+          <t xml:space="preserve">  ③ TikTok Shop / WESELL EC売上</t>
         </is>
       </c>
       <c r="B22" s="18" t="n">
@@ -1538,135 +1642,143 @@
         <v>0</v>
       </c>
       <c r="D22" s="18" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E22" s="18" t="n">
+        <v>66</v>
+      </c>
+      <c r="F22" s="18" t="n">
+        <v>150</v>
+      </c>
+      <c r="G22" s="18" t="n">
+        <v>292</v>
+      </c>
+      <c r="H22" s="18" t="n">
+        <v>490</v>
+      </c>
+      <c r="I22" s="18" t="n">
+        <v>720</v>
+      </c>
+      <c r="J22" s="18" t="n">
+        <v>975</v>
+      </c>
+      <c r="K22" s="18" t="n">
+        <v>1326</v>
+      </c>
+      <c r="L22" s="18" t="n">
+        <v>1760</v>
+      </c>
+      <c r="M22" s="18" t="n">
+        <v>2296</v>
+      </c>
+      <c r="N22" s="14" t="n">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     注文件数（件）</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="n">
         <v>50</v>
       </c>
-      <c r="F22" s="18" t="n">
-        <v>70</v>
-      </c>
-      <c r="G22" s="18" t="n">
-        <v>100</v>
-      </c>
-      <c r="H22" s="18" t="n">
-        <v>130</v>
-      </c>
-      <c r="I22" s="18" t="n">
-        <v>150</v>
-      </c>
-      <c r="J22" s="18" t="n">
-        <v>180</v>
-      </c>
-      <c r="K22" s="18" t="n">
-        <v>200</v>
-      </c>
-      <c r="L22" s="18" t="n">
-        <v>220</v>
-      </c>
-      <c r="M22" s="18" t="n">
-        <v>260</v>
-      </c>
-      <c r="N22" s="14" t="n">
-        <v>1380</v>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  コンテンツ制作費（タイアップ×10%）</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" s="18" t="n">
-        <v>25</v>
-      </c>
-      <c r="F23" s="18" t="n">
-        <v>35</v>
-      </c>
-      <c r="G23" s="18" t="n">
-        <v>50</v>
-      </c>
-      <c r="H23" s="18" t="n">
-        <v>65</v>
-      </c>
-      <c r="I23" s="18" t="n">
-        <v>75</v>
-      </c>
-      <c r="J23" s="18" t="n">
-        <v>90</v>
-      </c>
-      <c r="K23" s="18" t="n">
-        <v>100</v>
-      </c>
-      <c r="L23" s="18" t="n">
-        <v>110</v>
-      </c>
-      <c r="M23" s="18" t="n">
-        <v>130</v>
-      </c>
-      <c r="N23" s="14" t="n">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1">
+      <c r="E23" s="21" t="n">
+        <v>120</v>
+      </c>
+      <c r="F23" s="21" t="n">
+        <v>250</v>
+      </c>
+      <c r="G23" s="21" t="n">
+        <v>450</v>
+      </c>
+      <c r="H23" s="21" t="n">
+        <v>700</v>
+      </c>
+      <c r="I23" s="21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J23" s="21" t="n">
+        <v>1300</v>
+      </c>
+      <c r="K23" s="21" t="n">
+        <v>1700</v>
+      </c>
+      <c r="L23" s="21" t="n">
+        <v>2200</v>
+      </c>
+      <c r="M23" s="21" t="n">
+        <v>2800</v>
+      </c>
+      <c r="N23" s="22" t="n">
+        <v>10570</v>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
       <c r="A24" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  タイアップ原価合計</t>
-        </is>
-      </c>
-      <c r="B24" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="20" t="n">
-        <v>30</v>
-      </c>
-      <c r="E24" s="20" t="n">
-        <v>75</v>
-      </c>
-      <c r="F24" s="20" t="n">
-        <v>105</v>
-      </c>
-      <c r="G24" s="20" t="n">
-        <v>150</v>
-      </c>
-      <c r="H24" s="20" t="n">
-        <v>195</v>
-      </c>
-      <c r="I24" s="20" t="n">
-        <v>225</v>
-      </c>
-      <c r="J24" s="20" t="n">
-        <v>270</v>
-      </c>
-      <c r="K24" s="20" t="n">
-        <v>300</v>
-      </c>
-      <c r="L24" s="20" t="n">
-        <v>330</v>
-      </c>
-      <c r="M24" s="20" t="n">
-        <v>390</v>
-      </c>
-      <c r="N24" s="20" t="n">
-        <v>2070</v>
+          <t xml:space="preserve">     平均注文単価（円）</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E24" s="21" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F24" s="21" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G24" s="21" t="n">
+        <v>6500</v>
+      </c>
+      <c r="H24" s="21" t="n">
+        <v>7000</v>
+      </c>
+      <c r="I24" s="21" t="n">
+        <v>7200</v>
+      </c>
+      <c r="J24" s="21" t="n">
+        <v>7500</v>
+      </c>
+      <c r="K24" s="21" t="n">
+        <v>7800</v>
+      </c>
+      <c r="L24" s="21" t="n">
+        <v>8000</v>
+      </c>
+      <c r="M24" s="21" t="n">
+        <v>8200</v>
+      </c>
+      <c r="N24" s="22" t="n">
+        <v>6870</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  タイアップ粗利</t>
+          <t>売上合計</t>
         </is>
       </c>
       <c r="B25" s="26" t="n">
@@ -1676,925 +1788,1145 @@
         <v>0</v>
       </c>
       <c r="D25" s="26" t="n">
+        <v>125</v>
+      </c>
+      <c r="E25" s="26" t="n">
+        <v>316</v>
+      </c>
+      <c r="F25" s="26" t="n">
+        <v>500</v>
+      </c>
+      <c r="G25" s="26" t="n">
+        <v>792</v>
+      </c>
+      <c r="H25" s="26" t="n">
+        <v>1140</v>
+      </c>
+      <c r="I25" s="26" t="n">
+        <v>1470</v>
+      </c>
+      <c r="J25" s="26" t="n">
+        <v>1875</v>
+      </c>
+      <c r="K25" s="26" t="n">
+        <v>2326</v>
+      </c>
+      <c r="L25" s="26" t="n">
+        <v>2860</v>
+      </c>
+      <c r="M25" s="26" t="n">
+        <v>3596</v>
+      </c>
+      <c r="N25" s="26" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="26" ht="6" customHeight="1">
+      <c r="A26" s="27" t="inlineStr"/>
+      <c r="B26" s="28" t="n"/>
+      <c r="C26" s="28" t="n"/>
+      <c r="D26" s="28" t="n"/>
+      <c r="E26" s="28" t="n"/>
+      <c r="F26" s="28" t="n"/>
+      <c r="G26" s="28" t="n"/>
+      <c r="H26" s="28" t="n"/>
+      <c r="I26" s="28" t="n"/>
+      <c r="J26" s="28" t="n"/>
+      <c r="K26" s="28" t="n"/>
+      <c r="L26" s="28" t="n"/>
+      <c r="M26" s="28" t="n"/>
+      <c r="N26" s="28" t="n"/>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>【タイアップ原価】※ほぼライセンス料のみ</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="17" t="n"/>
+      <c r="E27" s="17" t="n"/>
+      <c r="F27" s="17" t="n"/>
+      <c r="G27" s="17" t="n"/>
+      <c r="H27" s="17" t="n"/>
+      <c r="I27" s="17" t="n"/>
+      <c r="J27" s="17" t="n"/>
+      <c r="K27" s="17" t="n"/>
+      <c r="L27" s="17" t="n"/>
+      <c r="M27" s="17" t="n"/>
+      <c r="N27" s="17" t="n"/>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ギャル協会ライセンス料（タイアップ×20%）</t>
+        </is>
+      </c>
+      <c r="B28" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="E28" s="18" t="n">
+        <v>50</v>
+      </c>
+      <c r="F28" s="18" t="n">
         <v>70</v>
       </c>
-      <c r="E25" s="26" t="n">
-        <v>175</v>
-      </c>
-      <c r="F25" s="26" t="n">
-        <v>245</v>
-      </c>
-      <c r="G25" s="26" t="n">
-        <v>350</v>
-      </c>
-      <c r="H25" s="26" t="n">
-        <v>455</v>
-      </c>
-      <c r="I25" s="26" t="n">
-        <v>525</v>
-      </c>
-      <c r="J25" s="26" t="n">
-        <v>630</v>
-      </c>
-      <c r="K25" s="26" t="n">
-        <v>700</v>
-      </c>
-      <c r="L25" s="26" t="n">
-        <v>770</v>
-      </c>
-      <c r="M25" s="26" t="n">
-        <v>910</v>
-      </c>
-      <c r="N25" s="26" t="n">
-        <v>4830</v>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  タイアップ粗利率</t>
-        </is>
-      </c>
-      <c r="B26" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="28" t="n">
-        <v>70</v>
-      </c>
-      <c r="E26" s="28" t="n">
-        <v>70</v>
-      </c>
-      <c r="F26" s="28" t="n">
-        <v>70</v>
-      </c>
-      <c r="G26" s="28" t="n">
-        <v>70</v>
-      </c>
-      <c r="H26" s="28" t="n">
-        <v>70</v>
-      </c>
-      <c r="I26" s="28" t="n">
-        <v>70</v>
-      </c>
-      <c r="J26" s="28" t="n">
-        <v>70</v>
-      </c>
-      <c r="K26" s="28" t="n">
-        <v>70</v>
-      </c>
-      <c r="L26" s="28" t="n">
-        <v>70</v>
-      </c>
-      <c r="M26" s="28" t="n">
-        <v>70</v>
-      </c>
-      <c r="N26" s="29" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="27" ht="6" customHeight="1">
-      <c r="A27" s="23" t="inlineStr"/>
-      <c r="B27" s="24" t="n"/>
-      <c r="C27" s="24" t="n"/>
-      <c r="D27" s="24" t="n"/>
-      <c r="E27" s="24" t="n"/>
-      <c r="F27" s="24" t="n"/>
-      <c r="G27" s="24" t="n"/>
-      <c r="H27" s="24" t="n"/>
-      <c r="I27" s="24" t="n"/>
-      <c r="J27" s="24" t="n"/>
-      <c r="K27" s="24" t="n"/>
-      <c r="L27" s="24" t="n"/>
-      <c r="M27" s="24" t="n"/>
-      <c r="N27" s="24" t="n"/>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="16" t="inlineStr">
-        <is>
-          <t>【TikTok Shop EC原価】</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="n"/>
-      <c r="C28" s="17" t="n"/>
-      <c r="D28" s="17" t="n"/>
-      <c r="E28" s="17" t="n"/>
-      <c r="F28" s="17" t="n"/>
-      <c r="G28" s="17" t="n"/>
-      <c r="H28" s="17" t="n"/>
-      <c r="I28" s="17" t="n"/>
-      <c r="J28" s="17" t="n"/>
-      <c r="K28" s="17" t="n"/>
-      <c r="L28" s="17" t="n"/>
-      <c r="M28" s="17" t="n"/>
-      <c r="N28" s="17" t="n"/>
+      <c r="G28" s="18" t="n">
+        <v>100</v>
+      </c>
+      <c r="H28" s="18" t="n">
+        <v>130</v>
+      </c>
+      <c r="I28" s="18" t="n">
+        <v>150</v>
+      </c>
+      <c r="J28" s="18" t="n">
+        <v>180</v>
+      </c>
+      <c r="K28" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="L28" s="18" t="n">
+        <v>220</v>
+      </c>
+      <c r="M28" s="18" t="n">
+        <v>260</v>
+      </c>
+      <c r="N28" s="14" t="n">
+        <v>1380</v>
+      </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">  コンテンツ制作費（タイアップ×10%）</t>
+        </is>
+      </c>
+      <c r="B29" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" s="18" t="n">
+        <v>25</v>
+      </c>
+      <c r="F29" s="18" t="n">
+        <v>35</v>
+      </c>
+      <c r="G29" s="18" t="n">
+        <v>50</v>
+      </c>
+      <c r="H29" s="18" t="n">
+        <v>65</v>
+      </c>
+      <c r="I29" s="18" t="n">
+        <v>75</v>
+      </c>
+      <c r="J29" s="18" t="n">
+        <v>90</v>
+      </c>
+      <c r="K29" s="18" t="n">
+        <v>100</v>
+      </c>
+      <c r="L29" s="18" t="n">
+        <v>110</v>
+      </c>
+      <c r="M29" s="18" t="n">
+        <v>130</v>
+      </c>
+      <c r="N29" s="14" t="n">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  タイアップ原価合計</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="24" t="n">
+        <v>30</v>
+      </c>
+      <c r="E30" s="24" t="n">
+        <v>75</v>
+      </c>
+      <c r="F30" s="24" t="n">
+        <v>105</v>
+      </c>
+      <c r="G30" s="24" t="n">
+        <v>150</v>
+      </c>
+      <c r="H30" s="24" t="n">
+        <v>195</v>
+      </c>
+      <c r="I30" s="24" t="n">
+        <v>225</v>
+      </c>
+      <c r="J30" s="24" t="n">
+        <v>270</v>
+      </c>
+      <c r="K30" s="24" t="n">
+        <v>300</v>
+      </c>
+      <c r="L30" s="24" t="n">
+        <v>330</v>
+      </c>
+      <c r="M30" s="24" t="n">
+        <v>390</v>
+      </c>
+      <c r="N30" s="24" t="n">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  タイアップ粗利</t>
+        </is>
+      </c>
+      <c r="B31" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="30" t="n">
+        <v>70</v>
+      </c>
+      <c r="E31" s="30" t="n">
+        <v>175</v>
+      </c>
+      <c r="F31" s="30" t="n">
+        <v>245</v>
+      </c>
+      <c r="G31" s="30" t="n">
+        <v>350</v>
+      </c>
+      <c r="H31" s="30" t="n">
+        <v>455</v>
+      </c>
+      <c r="I31" s="30" t="n">
+        <v>525</v>
+      </c>
+      <c r="J31" s="30" t="n">
+        <v>630</v>
+      </c>
+      <c r="K31" s="30" t="n">
+        <v>700</v>
+      </c>
+      <c r="L31" s="30" t="n">
+        <v>770</v>
+      </c>
+      <c r="M31" s="30" t="n">
+        <v>910</v>
+      </c>
+      <c r="N31" s="30" t="n">
+        <v>4830</v>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  タイアップ粗利率</t>
+        </is>
+      </c>
+      <c r="B32" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="32" t="n">
+        <v>70</v>
+      </c>
+      <c r="E32" s="32" t="n">
+        <v>70</v>
+      </c>
+      <c r="F32" s="32" t="n">
+        <v>70</v>
+      </c>
+      <c r="G32" s="32" t="n">
+        <v>70</v>
+      </c>
+      <c r="H32" s="32" t="n">
+        <v>70</v>
+      </c>
+      <c r="I32" s="32" t="n">
+        <v>70</v>
+      </c>
+      <c r="J32" s="32" t="n">
+        <v>70</v>
+      </c>
+      <c r="K32" s="32" t="n">
+        <v>70</v>
+      </c>
+      <c r="L32" s="32" t="n">
+        <v>70</v>
+      </c>
+      <c r="M32" s="32" t="n">
+        <v>70</v>
+      </c>
+      <c r="N32" s="33" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="33" ht="6" customHeight="1">
+      <c r="A33" s="27" t="inlineStr"/>
+      <c r="B33" s="28" t="n"/>
+      <c r="C33" s="28" t="n"/>
+      <c r="D33" s="28" t="n"/>
+      <c r="E33" s="28" t="n"/>
+      <c r="F33" s="28" t="n"/>
+      <c r="G33" s="28" t="n"/>
+      <c r="H33" s="28" t="n"/>
+      <c r="I33" s="28" t="n"/>
+      <c r="J33" s="28" t="n"/>
+      <c r="K33" s="28" t="n"/>
+      <c r="L33" s="28" t="n"/>
+      <c r="M33" s="28" t="n"/>
+      <c r="N33" s="28" t="n"/>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>【TikTok Shop EC原価】</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="n"/>
+      <c r="C34" s="17" t="n"/>
+      <c r="D34" s="17" t="n"/>
+      <c r="E34" s="17" t="n"/>
+      <c r="F34" s="17" t="n"/>
+      <c r="G34" s="17" t="n"/>
+      <c r="H34" s="17" t="n"/>
+      <c r="I34" s="17" t="n"/>
+      <c r="J34" s="17" t="n"/>
+      <c r="K34" s="17" t="n"/>
+      <c r="L34" s="17" t="n"/>
+      <c r="M34" s="17" t="n"/>
+      <c r="N34" s="17" t="n"/>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">  商品仕入れ原価（EC売上×45%）</t>
         </is>
       </c>
-      <c r="B29" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="18" t="n">
+      <c r="B35" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="18" t="n">
         <v>11</v>
       </c>
-      <c r="E29" s="18" t="n">
+      <c r="E35" s="18" t="n">
         <v>30</v>
       </c>
-      <c r="F29" s="18" t="n">
+      <c r="F35" s="18" t="n">
         <v>68</v>
       </c>
-      <c r="G29" s="18" t="n">
+      <c r="G35" s="18" t="n">
         <v>131</v>
       </c>
-      <c r="H29" s="18" t="n">
+      <c r="H35" s="18" t="n">
         <v>220</v>
       </c>
-      <c r="I29" s="18" t="n">
+      <c r="I35" s="18" t="n">
         <v>324</v>
       </c>
-      <c r="J29" s="18" t="n">
+      <c r="J35" s="18" t="n">
         <v>439</v>
       </c>
-      <c r="K29" s="18" t="n">
+      <c r="K35" s="18" t="n">
         <v>597</v>
       </c>
-      <c r="L29" s="18" t="n">
+      <c r="L35" s="18" t="n">
         <v>792</v>
       </c>
-      <c r="M29" s="18" t="n">
+      <c r="M35" s="18" t="n">
         <v>1033</v>
       </c>
-      <c r="N29" s="14" t="n">
+      <c r="N35" s="14" t="n">
         <v>3645</v>
       </c>
     </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="11" t="inlineStr">
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  TikTok Shop手数料（EC売上×6%）</t>
         </is>
       </c>
-      <c r="B30" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="18" t="n">
+      <c r="B36" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E30" s="18" t="n">
+      <c r="E36" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="F30" s="18" t="n">
+      <c r="F36" s="18" t="n">
         <v>9</v>
       </c>
-      <c r="G30" s="18" t="n">
+      <c r="G36" s="18" t="n">
         <v>18</v>
       </c>
-      <c r="H30" s="18" t="n">
+      <c r="H36" s="18" t="n">
         <v>29</v>
       </c>
-      <c r="I30" s="18" t="n">
+      <c r="I36" s="18" t="n">
         <v>43</v>
       </c>
-      <c r="J30" s="18" t="n">
+      <c r="J36" s="18" t="n">
         <v>58</v>
       </c>
-      <c r="K30" s="18" t="n">
+      <c r="K36" s="18" t="n">
         <v>80</v>
       </c>
-      <c r="L30" s="18" t="n">
+      <c r="L36" s="18" t="n">
         <v>106</v>
       </c>
-      <c r="M30" s="18" t="n">
+      <c r="M36" s="18" t="n">
         <v>138</v>
       </c>
-      <c r="N30" s="14" t="n">
+      <c r="N36" s="14" t="n">
         <v>487</v>
       </c>
     </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="11" t="inlineStr">
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  ギャル協会RS・物販（EC売上×15%）</t>
         </is>
       </c>
-      <c r="B31" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="18" t="n">
+      <c r="B37" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E31" s="18" t="n">
+      <c r="E37" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="F31" s="18" t="n">
+      <c r="F37" s="18" t="n">
         <v>22</v>
       </c>
-      <c r="G31" s="18" t="n">
+      <c r="G37" s="18" t="n">
         <v>44</v>
       </c>
-      <c r="H31" s="18" t="n">
+      <c r="H37" s="18" t="n">
         <v>74</v>
       </c>
-      <c r="I31" s="18" t="n">
+      <c r="I37" s="18" t="n">
         <v>108</v>
       </c>
-      <c r="J31" s="18" t="n">
+      <c r="J37" s="18" t="n">
         <v>146</v>
       </c>
-      <c r="K31" s="18" t="n">
+      <c r="K37" s="18" t="n">
         <v>199</v>
       </c>
-      <c r="L31" s="18" t="n">
+      <c r="L37" s="18" t="n">
         <v>264</v>
       </c>
-      <c r="M31" s="18" t="n">
+      <c r="M37" s="18" t="n">
         <v>344</v>
       </c>
-      <c r="N31" s="14" t="n">
+      <c r="N37" s="14" t="n">
         <v>1215</v>
       </c>
     </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="19" t="inlineStr">
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  EC原価合計</t>
         </is>
       </c>
-      <c r="B32" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="20" t="n">
+      <c r="B38" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="24" t="n">
         <v>17</v>
       </c>
-      <c r="E32" s="20" t="n">
+      <c r="E38" s="24" t="n">
         <v>44</v>
       </c>
-      <c r="F32" s="20" t="n">
+      <c r="F38" s="24" t="n">
         <v>99</v>
       </c>
-      <c r="G32" s="20" t="n">
+      <c r="G38" s="24" t="n">
         <v>193</v>
       </c>
-      <c r="H32" s="20" t="n">
+      <c r="H38" s="24" t="n">
         <v>323</v>
       </c>
-      <c r="I32" s="20" t="n">
+      <c r="I38" s="24" t="n">
         <v>475</v>
       </c>
-      <c r="J32" s="20" t="n">
+      <c r="J38" s="24" t="n">
         <v>643</v>
       </c>
-      <c r="K32" s="20" t="n">
+      <c r="K38" s="24" t="n">
         <v>876</v>
       </c>
-      <c r="L32" s="20" t="n">
+      <c r="L38" s="24" t="n">
         <v>1162</v>
       </c>
-      <c r="M32" s="20" t="n">
+      <c r="M38" s="24" t="n">
         <v>1515</v>
       </c>
-      <c r="N32" s="20" t="n">
+      <c r="N38" s="24" t="n">
         <v>5347</v>
       </c>
     </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="30" t="inlineStr">
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  TikTok Shop 粗利</t>
         </is>
       </c>
-      <c r="B33" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="31" t="n">
+      <c r="B39" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="E33" s="31" t="n">
+      <c r="E39" s="35" t="n">
         <v>22</v>
       </c>
-      <c r="F33" s="31" t="n">
+      <c r="F39" s="35" t="n">
         <v>51</v>
       </c>
-      <c r="G33" s="31" t="n">
+      <c r="G39" s="35" t="n">
         <v>99</v>
       </c>
-      <c r="H33" s="31" t="n">
+      <c r="H39" s="35" t="n">
         <v>167</v>
       </c>
-      <c r="I33" s="31" t="n">
+      <c r="I39" s="35" t="n">
         <v>245</v>
       </c>
-      <c r="J33" s="31" t="n">
+      <c r="J39" s="35" t="n">
         <v>332</v>
       </c>
-      <c r="K33" s="31" t="n">
+      <c r="K39" s="35" t="n">
         <v>450</v>
       </c>
-      <c r="L33" s="31" t="n">
+      <c r="L39" s="35" t="n">
         <v>598</v>
       </c>
-      <c r="M33" s="31" t="n">
+      <c r="M39" s="35" t="n">
         <v>781</v>
       </c>
-      <c r="N33" s="31" t="n">
+      <c r="N39" s="35" t="n">
         <v>2753</v>
       </c>
     </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="27" t="inlineStr">
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  TikTok Shop 粗利率</t>
         </is>
       </c>
-      <c r="B34" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="28" t="n">
+      <c r="B40" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="32" t="n">
         <v>32</v>
       </c>
-      <c r="E34" s="28" t="n">
+      <c r="E40" s="32" t="n">
         <v>33.3</v>
       </c>
-      <c r="F34" s="28" t="n">
+      <c r="F40" s="32" t="n">
         <v>34</v>
       </c>
-      <c r="G34" s="28" t="n">
+      <c r="G40" s="32" t="n">
         <v>33.9</v>
       </c>
-      <c r="H34" s="28" t="n">
+      <c r="H40" s="32" t="n">
         <v>34.1</v>
       </c>
-      <c r="I34" s="28" t="n">
+      <c r="I40" s="32" t="n">
         <v>34</v>
       </c>
-      <c r="J34" s="28" t="n">
+      <c r="J40" s="32" t="n">
         <v>34.1</v>
       </c>
-      <c r="K34" s="28" t="n">
+      <c r="K40" s="32" t="n">
         <v>33.9</v>
       </c>
-      <c r="L34" s="28" t="n">
+      <c r="L40" s="32" t="n">
         <v>34</v>
       </c>
-      <c r="M34" s="28" t="n">
+      <c r="M40" s="32" t="n">
         <v>34</v>
       </c>
-      <c r="N34" s="29" t="n">
+      <c r="N40" s="33" t="n">
         <v>33.7</v>
       </c>
     </row>
-    <row r="35" ht="6" customHeight="1">
-      <c r="A35" s="23" t="inlineStr"/>
-      <c r="B35" s="24" t="n"/>
-      <c r="C35" s="24" t="n"/>
-      <c r="D35" s="24" t="n"/>
-      <c r="E35" s="24" t="n"/>
-      <c r="F35" s="24" t="n"/>
-      <c r="G35" s="24" t="n"/>
-      <c r="H35" s="24" t="n"/>
-      <c r="I35" s="24" t="n"/>
-      <c r="J35" s="24" t="n"/>
-      <c r="K35" s="24" t="n"/>
-      <c r="L35" s="24" t="n"/>
-      <c r="M35" s="24" t="n"/>
-      <c r="N35" s="24" t="n"/>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="32" t="inlineStr">
+    <row r="41" ht="6" customHeight="1">
+      <c r="A41" s="27" t="inlineStr"/>
+      <c r="B41" s="28" t="n"/>
+      <c r="C41" s="28" t="n"/>
+      <c r="D41" s="28" t="n"/>
+      <c r="E41" s="28" t="n"/>
+      <c r="F41" s="28" t="n"/>
+      <c r="G41" s="28" t="n"/>
+      <c r="H41" s="28" t="n"/>
+      <c r="I41" s="28" t="n"/>
+      <c r="J41" s="28" t="n"/>
+      <c r="K41" s="28" t="n"/>
+      <c r="L41" s="28" t="n"/>
+      <c r="M41" s="28" t="n"/>
+      <c r="N41" s="28" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="36" t="inlineStr">
         <is>
           <t>売上原価合計</t>
         </is>
       </c>
-      <c r="B36" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="33" t="n">
+      <c r="B42" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="37" t="n">
         <v>47</v>
       </c>
-      <c r="E36" s="33" t="n">
+      <c r="E42" s="37" t="n">
         <v>119</v>
       </c>
-      <c r="F36" s="33" t="n">
+      <c r="F42" s="37" t="n">
         <v>204</v>
       </c>
-      <c r="G36" s="33" t="n">
+      <c r="G42" s="37" t="n">
         <v>343</v>
       </c>
-      <c r="H36" s="33" t="n">
+      <c r="H42" s="37" t="n">
         <v>518</v>
       </c>
-      <c r="I36" s="33" t="n">
+      <c r="I42" s="37" t="n">
         <v>700</v>
       </c>
-      <c r="J36" s="33" t="n">
+      <c r="J42" s="37" t="n">
         <v>913</v>
       </c>
-      <c r="K36" s="33" t="n">
+      <c r="K42" s="37" t="n">
         <v>1176</v>
       </c>
-      <c r="L36" s="33" t="n">
+      <c r="L42" s="37" t="n">
         <v>1492</v>
       </c>
-      <c r="M36" s="33" t="n">
+      <c r="M42" s="37" t="n">
         <v>1905</v>
       </c>
-      <c r="N36" s="33" t="n">
+      <c r="N42" s="37" t="n">
         <v>7417</v>
       </c>
     </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="34" t="inlineStr">
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="38" t="inlineStr">
         <is>
           <t>粗利益合計</t>
         </is>
       </c>
-      <c r="B37" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C37" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="35" t="n">
+      <c r="B43" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="39" t="n">
         <v>78</v>
       </c>
-      <c r="E37" s="35" t="n">
+      <c r="E43" s="39" t="n">
         <v>197</v>
       </c>
-      <c r="F37" s="35" t="n">
+      <c r="F43" s="39" t="n">
         <v>296</v>
       </c>
-      <c r="G37" s="35" t="n">
+      <c r="G43" s="39" t="n">
         <v>449</v>
       </c>
-      <c r="H37" s="35" t="n">
+      <c r="H43" s="39" t="n">
         <v>622</v>
       </c>
-      <c r="I37" s="35" t="n">
+      <c r="I43" s="39" t="n">
         <v>770</v>
       </c>
-      <c r="J37" s="35" t="n">
+      <c r="J43" s="39" t="n">
         <v>962</v>
       </c>
-      <c r="K37" s="35" t="n">
+      <c r="K43" s="39" t="n">
         <v>1150</v>
       </c>
-      <c r="L37" s="35" t="n">
+      <c r="L43" s="39" t="n">
         <v>1368</v>
       </c>
-      <c r="M37" s="35" t="n">
+      <c r="M43" s="39" t="n">
         <v>1691</v>
       </c>
-      <c r="N37" s="35" t="n">
+      <c r="N43" s="39" t="n">
         <v>7583</v>
       </c>
     </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="27" t="inlineStr">
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="31" t="inlineStr">
         <is>
           <t>粗利率（合計）</t>
         </is>
       </c>
-      <c r="B38" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="28" t="n">
+      <c r="B44" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="32" t="n">
         <v>62.4</v>
       </c>
-      <c r="E38" s="28" t="n">
+      <c r="E44" s="32" t="n">
         <v>62.3</v>
       </c>
-      <c r="F38" s="28" t="n">
+      <c r="F44" s="32" t="n">
         <v>59.2</v>
       </c>
-      <c r="G38" s="28" t="n">
+      <c r="G44" s="32" t="n">
         <v>56.7</v>
       </c>
-      <c r="H38" s="28" t="n">
+      <c r="H44" s="32" t="n">
         <v>54.6</v>
       </c>
-      <c r="I38" s="28" t="n">
+      <c r="I44" s="32" t="n">
         <v>52.4</v>
       </c>
-      <c r="J38" s="28" t="n">
+      <c r="J44" s="32" t="n">
         <v>51.3</v>
       </c>
-      <c r="K38" s="28" t="n">
+      <c r="K44" s="32" t="n">
         <v>49.4</v>
       </c>
-      <c r="L38" s="28" t="n">
+      <c r="L44" s="32" t="n">
         <v>47.8</v>
       </c>
-      <c r="M38" s="28" t="n">
+      <c r="M44" s="32" t="n">
         <v>47</v>
       </c>
-      <c r="N38" s="29" t="n">
+      <c r="N44" s="33" t="n">
         <v>54.3</v>
       </c>
     </row>
-    <row r="39" ht="6" customHeight="1">
-      <c r="A39" s="23" t="inlineStr"/>
-      <c r="B39" s="24" t="n"/>
-      <c r="C39" s="24" t="n"/>
-      <c r="D39" s="24" t="n"/>
-      <c r="E39" s="24" t="n"/>
-      <c r="F39" s="24" t="n"/>
-      <c r="G39" s="24" t="n"/>
-      <c r="H39" s="24" t="n"/>
-      <c r="I39" s="24" t="n"/>
-      <c r="J39" s="24" t="n"/>
-      <c r="K39" s="24" t="n"/>
-      <c r="L39" s="24" t="n"/>
-      <c r="M39" s="24" t="n"/>
-      <c r="N39" s="24" t="n"/>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="16" t="inlineStr">
+    <row r="45" ht="6" customHeight="1">
+      <c r="A45" s="27" t="inlineStr"/>
+      <c r="B45" s="28" t="n"/>
+      <c r="C45" s="28" t="n"/>
+      <c r="D45" s="28" t="n"/>
+      <c r="E45" s="28" t="n"/>
+      <c r="F45" s="28" t="n"/>
+      <c r="G45" s="28" t="n"/>
+      <c r="H45" s="28" t="n"/>
+      <c r="I45" s="28" t="n"/>
+      <c r="J45" s="28" t="n"/>
+      <c r="K45" s="28" t="n"/>
+      <c r="L45" s="28" t="n"/>
+      <c r="M45" s="28" t="n"/>
+      <c r="N45" s="28" t="n"/>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="16" t="inlineStr">
         <is>
           <t>【販売管理費】</t>
         </is>
       </c>
-      <c r="B40" s="17" t="n"/>
-      <c r="C40" s="17" t="n"/>
-      <c r="D40" s="17" t="n"/>
-      <c r="E40" s="17" t="n"/>
-      <c r="F40" s="17" t="n"/>
-      <c r="G40" s="17" t="n"/>
-      <c r="H40" s="17" t="n"/>
-      <c r="I40" s="17" t="n"/>
-      <c r="J40" s="17" t="n"/>
-      <c r="K40" s="17" t="n"/>
-      <c r="L40" s="17" t="n"/>
-      <c r="M40" s="17" t="n"/>
-      <c r="N40" s="17" t="n"/>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="11" t="inlineStr">
+      <c r="B46" s="17" t="n"/>
+      <c r="C46" s="17" t="n"/>
+      <c r="D46" s="17" t="n"/>
+      <c r="E46" s="17" t="n"/>
+      <c r="F46" s="17" t="n"/>
+      <c r="G46" s="17" t="n"/>
+      <c r="H46" s="17" t="n"/>
+      <c r="I46" s="17" t="n"/>
+      <c r="J46" s="17" t="n"/>
+      <c r="K46" s="17" t="n"/>
+      <c r="L46" s="17" t="n"/>
+      <c r="M46" s="17" t="n"/>
+      <c r="N46" s="17" t="n"/>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  広告費（TK/IG広告運用）</t>
         </is>
       </c>
-      <c r="B41" s="18" t="n">
+      <c r="B47" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="C41" s="18" t="n">
+      <c r="C47" s="18" t="n">
         <v>150</v>
       </c>
-      <c r="D41" s="18" t="n">
+      <c r="D47" s="18" t="n">
         <v>150</v>
       </c>
-      <c r="E41" s="18" t="n">
+      <c r="E47" s="18" t="n">
         <v>150</v>
       </c>
-      <c r="F41" s="18" t="n">
+      <c r="F47" s="18" t="n">
         <v>200</v>
       </c>
-      <c r="G41" s="18" t="n">
+      <c r="G47" s="18" t="n">
         <v>200</v>
       </c>
-      <c r="H41" s="18" t="n">
+      <c r="H47" s="18" t="n">
         <v>250</v>
       </c>
-      <c r="I41" s="18" t="n">
+      <c r="I47" s="18" t="n">
         <v>250</v>
       </c>
-      <c r="J41" s="18" t="n">
+      <c r="J47" s="18" t="n">
         <v>250</v>
       </c>
-      <c r="K41" s="18" t="n">
+      <c r="K47" s="18" t="n">
         <v>250</v>
       </c>
-      <c r="L41" s="18" t="n">
+      <c r="L47" s="18" t="n">
         <v>250</v>
       </c>
-      <c r="M41" s="18" t="n">
+      <c r="M47" s="18" t="n">
         <v>250</v>
       </c>
-      <c r="N41" s="14" t="n">
+      <c r="N47" s="14" t="n">
         <v>2450</v>
       </c>
     </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="11" t="inlineStr">
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  人件費（バズ社員 ／ ENTIALはゼロ）</t>
         </is>
       </c>
-      <c r="B42" s="18" t="n">
+      <c r="B48" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="C42" s="18" t="n">
+      <c r="C48" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="D42" s="18" t="n">
+      <c r="D48" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="E42" s="18" t="n">
+      <c r="E48" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="F42" s="18" t="n">
+      <c r="F48" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="G42" s="18" t="n">
+      <c r="G48" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="H42" s="18" t="n">
+      <c r="H48" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="I42" s="18" t="n">
+      <c r="I48" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="J42" s="18" t="n">
+      <c r="J48" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="K42" s="18" t="n">
+      <c r="K48" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="L42" s="18" t="n">
+      <c r="L48" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="M42" s="18" t="n">
+      <c r="M48" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="N42" s="14" t="n">
+      <c r="N48" s="14" t="n">
         <v>1200</v>
       </c>
     </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="11" t="inlineStr">
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  その他販管費</t>
         </is>
       </c>
-      <c r="B43" s="18" t="n">
+      <c r="B49" s="18" t="n">
         <v>50</v>
       </c>
-      <c r="C43" s="18" t="n">
+      <c r="C49" s="18" t="n">
         <v>50</v>
       </c>
-      <c r="D43" s="18" t="n">
+      <c r="D49" s="18" t="n">
         <v>50</v>
       </c>
-      <c r="E43" s="18" t="n">
+      <c r="E49" s="18" t="n">
         <v>60</v>
       </c>
-      <c r="F43" s="18" t="n">
+      <c r="F49" s="18" t="n">
         <v>60</v>
       </c>
-      <c r="G43" s="18" t="n">
+      <c r="G49" s="18" t="n">
         <v>60</v>
       </c>
-      <c r="H43" s="18" t="n">
+      <c r="H49" s="18" t="n">
         <v>70</v>
       </c>
-      <c r="I43" s="18" t="n">
+      <c r="I49" s="18" t="n">
         <v>70</v>
       </c>
-      <c r="J43" s="18" t="n">
+      <c r="J49" s="18" t="n">
         <v>80</v>
       </c>
-      <c r="K43" s="18" t="n">
+      <c r="K49" s="18" t="n">
         <v>80</v>
       </c>
-      <c r="L43" s="18" t="n">
+      <c r="L49" s="18" t="n">
         <v>90</v>
       </c>
-      <c r="M43" s="18" t="n">
+      <c r="M49" s="18" t="n">
         <v>90</v>
       </c>
-      <c r="N43" s="14" t="n">
+      <c r="N49" s="14" t="n">
         <v>810</v>
       </c>
     </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="32" t="inlineStr">
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="36" t="inlineStr">
         <is>
           <t>販売管理費合計</t>
         </is>
       </c>
-      <c r="B44" s="33" t="n">
+      <c r="B50" s="37" t="n">
         <v>250</v>
       </c>
-      <c r="C44" s="33" t="n">
+      <c r="C50" s="37" t="n">
         <v>300</v>
       </c>
-      <c r="D44" s="33" t="n">
+      <c r="D50" s="37" t="n">
         <v>300</v>
       </c>
-      <c r="E44" s="33" t="n">
+      <c r="E50" s="37" t="n">
         <v>310</v>
       </c>
-      <c r="F44" s="33" t="n">
+      <c r="F50" s="37" t="n">
         <v>360</v>
       </c>
-      <c r="G44" s="33" t="n">
+      <c r="G50" s="37" t="n">
         <v>360</v>
       </c>
-      <c r="H44" s="33" t="n">
+      <c r="H50" s="37" t="n">
         <v>420</v>
       </c>
-      <c r="I44" s="33" t="n">
+      <c r="I50" s="37" t="n">
         <v>420</v>
       </c>
-      <c r="J44" s="33" t="n">
+      <c r="J50" s="37" t="n">
         <v>430</v>
       </c>
-      <c r="K44" s="33" t="n">
+      <c r="K50" s="37" t="n">
         <v>430</v>
       </c>
-      <c r="L44" s="33" t="n">
+      <c r="L50" s="37" t="n">
         <v>440</v>
       </c>
-      <c r="M44" s="33" t="n">
+      <c r="M50" s="37" t="n">
         <v>440</v>
       </c>
-      <c r="N44" s="33" t="n">
+      <c r="N50" s="37" t="n">
         <v>4460</v>
       </c>
     </row>
-    <row r="45" ht="6" customHeight="1">
-      <c r="A45" s="23" t="inlineStr"/>
-      <c r="B45" s="24" t="n"/>
-      <c r="C45" s="24" t="n"/>
-      <c r="D45" s="24" t="n"/>
-      <c r="E45" s="24" t="n"/>
-      <c r="F45" s="24" t="n"/>
-      <c r="G45" s="24" t="n"/>
-      <c r="H45" s="24" t="n"/>
-      <c r="I45" s="24" t="n"/>
-      <c r="J45" s="24" t="n"/>
-      <c r="K45" s="24" t="n"/>
-      <c r="L45" s="24" t="n"/>
-      <c r="M45" s="24" t="n"/>
-      <c r="N45" s="24" t="n"/>
-    </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="15" t="inlineStr">
+    <row r="51" ht="6" customHeight="1">
+      <c r="A51" s="27" t="inlineStr"/>
+      <c r="B51" s="28" t="n"/>
+      <c r="C51" s="28" t="n"/>
+      <c r="D51" s="28" t="n"/>
+      <c r="E51" s="28" t="n"/>
+      <c r="F51" s="28" t="n"/>
+      <c r="G51" s="28" t="n"/>
+      <c r="H51" s="28" t="n"/>
+      <c r="I51" s="28" t="n"/>
+      <c r="J51" s="28" t="n"/>
+      <c r="K51" s="28" t="n"/>
+      <c r="L51" s="28" t="n"/>
+      <c r="M51" s="28" t="n"/>
+      <c r="N51" s="28" t="n"/>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="15" t="inlineStr">
         <is>
           <t>営業利益</t>
         </is>
       </c>
-      <c r="B46" s="36" t="n">
+      <c r="B52" s="40" t="n">
         <v>-250</v>
       </c>
-      <c r="C46" s="36" t="n">
+      <c r="C52" s="40" t="n">
         <v>-300</v>
       </c>
-      <c r="D46" s="36" t="n">
+      <c r="D52" s="40" t="n">
         <v>-222</v>
       </c>
-      <c r="E46" s="36" t="n">
+      <c r="E52" s="40" t="n">
         <v>-113</v>
       </c>
-      <c r="F46" s="36" t="n">
+      <c r="F52" s="40" t="n">
         <v>-64</v>
       </c>
-      <c r="G46" s="37" t="n">
+      <c r="G52" s="41" t="n">
         <v>89</v>
       </c>
-      <c r="H46" s="36" t="n">
+      <c r="H52" s="40" t="n">
         <v>202</v>
       </c>
-      <c r="I46" s="36" t="n">
+      <c r="I52" s="40" t="n">
         <v>350</v>
       </c>
-      <c r="J46" s="36" t="n">
+      <c r="J52" s="40" t="n">
         <v>532</v>
       </c>
-      <c r="K46" s="36" t="n">
+      <c r="K52" s="40" t="n">
         <v>720</v>
       </c>
-      <c r="L46" s="36" t="n">
+      <c r="L52" s="40" t="n">
         <v>928</v>
       </c>
-      <c r="M46" s="36" t="n">
+      <c r="M52" s="40" t="n">
         <v>1251</v>
       </c>
-      <c r="N46" s="37" t="n">
+      <c r="N52" s="41" t="n">
         <v>3123</v>
       </c>
     </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="27" t="inlineStr">
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="31" t="inlineStr">
         <is>
           <t>営業利益率</t>
         </is>
       </c>
-      <c r="B47" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="C47" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" s="28" t="n">
+      <c r="B53" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="32" t="n">
         <v>-177.6</v>
       </c>
-      <c r="E47" s="28" t="n">
+      <c r="E53" s="32" t="n">
         <v>-35.8</v>
       </c>
-      <c r="F47" s="28" t="n">
+      <c r="F53" s="32" t="n">
         <v>-12.8</v>
       </c>
-      <c r="G47" s="28" t="n">
+      <c r="G53" s="32" t="n">
         <v>11.2</v>
       </c>
-      <c r="H47" s="28" t="n">
+      <c r="H53" s="32" t="n">
         <v>17.7</v>
       </c>
-      <c r="I47" s="28" t="n">
+      <c r="I53" s="32" t="n">
         <v>23.8</v>
       </c>
-      <c r="J47" s="28" t="n">
+      <c r="J53" s="32" t="n">
         <v>28.4</v>
       </c>
-      <c r="K47" s="28" t="n">
+      <c r="K53" s="32" t="n">
         <v>31</v>
       </c>
-      <c r="L47" s="28" t="n">
+      <c r="L53" s="32" t="n">
         <v>32.4</v>
       </c>
-      <c r="M47" s="28" t="n">
+      <c r="M53" s="32" t="n">
         <v>34.8</v>
       </c>
-      <c r="N47" s="29" t="n">
+      <c r="N53" s="33" t="n">
         <v>-4.7</v>
       </c>
     </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="38" t="inlineStr">
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="42" t="inlineStr">
         <is>
           <t>★ 損益分岐：M6 から黒字転換（営業利益行の緑セル）　Year1通期営業利益：3,123万円　Year1売上：15,000万円</t>
         </is>
       </c>
-      <c r="B48" s="5" t="n"/>
-      <c r="C48" s="5" t="n"/>
-      <c r="D48" s="5" t="n"/>
-      <c r="E48" s="5" t="n"/>
-      <c r="F48" s="5" t="n"/>
-      <c r="G48" s="5" t="n"/>
-      <c r="H48" s="5" t="n"/>
-      <c r="I48" s="5" t="n"/>
-      <c r="J48" s="5" t="n"/>
-      <c r="K48" s="5" t="n"/>
-      <c r="L48" s="5" t="n"/>
-      <c r="M48" s="5" t="n"/>
-      <c r="N48" s="5" t="n"/>
-    </row>
-    <row r="49" ht="14" customHeight="1">
-      <c r="A49" s="39" t="inlineStr">
+      <c r="B54" s="5" t="n"/>
+      <c r="C54" s="5" t="n"/>
+      <c r="D54" s="5" t="n"/>
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="5" t="n"/>
+      <c r="G54" s="5" t="n"/>
+      <c r="H54" s="5" t="n"/>
+      <c r="I54" s="5" t="n"/>
+      <c r="J54" s="5" t="n"/>
+      <c r="K54" s="5" t="n"/>
+      <c r="L54" s="5" t="n"/>
+      <c r="M54" s="5" t="n"/>
+      <c r="N54" s="5" t="n"/>
+    </row>
+    <row r="55" ht="14" customHeight="1">
+      <c r="A55" s="43" t="inlineStr">
         <is>
           <t>【注記】 単位：万円　／ タイアップ原価：ライセンス料20%＋制作費10%＝計30%　／ EC原価：商品仕入45%＋TK手数料6%＋ギャル協会RS15%＝計66%　／ ENTIALへの費用はバズPLに計上なし（別途協議）</t>
         </is>
       </c>
-      <c r="B49" s="5" t="n"/>
-      <c r="C49" s="5" t="n"/>
-      <c r="D49" s="5" t="n"/>
-      <c r="E49" s="5" t="n"/>
-      <c r="F49" s="5" t="n"/>
-      <c r="G49" s="5" t="n"/>
-      <c r="H49" s="5" t="n"/>
-      <c r="I49" s="5" t="n"/>
-      <c r="J49" s="5" t="n"/>
-      <c r="K49" s="5" t="n"/>
-      <c r="L49" s="5" t="n"/>
-      <c r="M49" s="5" t="n"/>
-      <c r="N49" s="5" t="n"/>
+      <c r="B55" s="5" t="n"/>
+      <c r="C55" s="5" t="n"/>
+      <c r="D55" s="5" t="n"/>
+      <c r="E55" s="5" t="n"/>
+      <c r="F55" s="5" t="n"/>
+      <c r="G55" s="5" t="n"/>
+      <c r="H55" s="5" t="n"/>
+      <c r="I55" s="5" t="n"/>
+      <c r="J55" s="5" t="n"/>
+      <c r="K55" s="5" t="n"/>
+      <c r="L55" s="5" t="n"/>
+      <c r="M55" s="5" t="n"/>
+      <c r="N55" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A55:N55"/>
     <mergeCell ref="A4:N4"/>
-    <mergeCell ref="A48:N48"/>
+    <mergeCell ref="A54:N54"/>
     <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A49:N49"/>
     <mergeCell ref="A13:N13"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
